--- a/zy72136/uploads/meal_allowance_preview.xlsx
+++ b/zy72136/uploads/meal_allowance_preview.xlsx
@@ -493,31 +493,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TRK-C01</t>
+          <t>TRK-001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>红旗颂</t>
+          <t>黄河大合唱</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>杭州大剧院</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>北京国家大剧院</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E2" t="n">
+        <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>3840</v>
+        <v>3600</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -526,7 +522,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>林老师指定开场曲</t>
+          <t>林老师指定曲目，合唱团巡演餐补表重点关注</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -536,7 +532,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>合唱团巡演餐补台账_CSV.csv</t>
+          <t>合唱团巡演曲目表.xlsx</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -549,50 +545,46 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TRK-C02</t>
+          <t>TRK-002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>我和我的祖国</t>
+          <t>茉莉花</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>杭州大剧院</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>北京国家大剧院</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E3" t="n">
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>3200</v>
+        <v>2400</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>可发放</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>旧版母带，2023年录音</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>编号重复</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>合唱团巡演餐补台账_CSV.csv</t>
+          <t>合唱团巡演曲目表.xlsx</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -605,50 +597,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TRK-C03</t>
+          <t>TRK-002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>团结就是力量</t>
+          <t>茉莉花</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>杭州大剧院</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>北京国家大剧院</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>32</v>
+      </c>
+      <c r="E4" t="n">
+        <v>80</v>
       </c>
       <c r="F4" t="n">
-        <v>2800</v>
+        <v>2560</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>可发放</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>旧版母带</t>
+          <t>重复曲目编号TRK-002，注意核对</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>编号重复</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>合唱团巡演餐补台账_CSV.csv</t>
+          <t>合唱团巡演曲目表.xlsx</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -661,31 +649,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TRK-C04</t>
+          <t>TRK-003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>保卫黄河</t>
+          <t>在希望的田野上</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>杭州大剧院</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>北京国家大剧院</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>38</v>
+      </c>
+      <c r="E5" t="n">
+        <v>80</v>
       </c>
       <c r="F5" t="n">
-        <v>3360</v>
+        <v>3040</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -694,7 +678,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>缺授权 合唱团巡演餐补表待确认</t>
+          <t>缺授权，合唱团巡演餐补表待林老师确认</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -704,7 +688,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>合唱团巡演餐补台账_CSV.csv</t>
+          <t>合唱团巡演曲目表.xlsx</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -717,31 +701,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TRK-C05</t>
+          <t>TRK-004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>映山红</t>
+          <t>歌唱祖国</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>南京保利剧院</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>上海音乐厅</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>50</v>
+      </c>
+      <c r="E6" t="n">
+        <v>80</v>
       </c>
       <c r="F6" t="n">
-        <v>3040</v>
+        <v>4000</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -750,7 +730,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>授权过期</t>
+          <t>授权已过期，请更新</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -760,7 +740,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>合唱团巡演餐补台账_CSV.csv</t>
+          <t>合唱团巡演曲目表.xlsx</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -773,24 +753,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TRK-C06</t>
+          <t>TRK-005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>美丽的草原我的家</t>
+          <t>我爱你中国</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>南京保利剧院</t>
+          <t>上海音乐厅</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+      <c r="E7" t="n">
+        <v>80</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
@@ -800,7 +778,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>参演人数空值</t>
+          <t>参演人数空值，需要补全</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -810,7 +788,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>合唱团巡演餐补台账_CSV.csv</t>
+          <t>合唱团巡演曲目表.xlsx</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -823,50 +801,42 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TRK-C07</t>
+          <t>TRK-006</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>在太行山上</t>
+          <t>天路（女声版</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>南京保利剧院</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>2400</v>
-      </c>
+          <t>上海音乐厅</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>25</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>可发放</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>旧版典藏</t>
+          <t>餐补标准空值</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>信息不全</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>合唱团巡演餐补台账_CSV.csv</t>
+          <t>合唱团巡演曲目表.xlsx</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -879,44 +849,46 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TRK-C08</t>
+          <t>TRK-007</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>游击队歌</t>
+          <t>青藏高原</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>南京保利剧院</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>广州大剧院</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>28</v>
+      </c>
+      <c r="E9" t="n">
+        <v>80</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2240</v>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>可发放</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>餐补标准空值</t>
+          <t>旧版母带，2022年</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>信息不全</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>合唱团巡演餐补台账_CSV.csv</t>
+          <t>合唱团巡演曲目表.xlsx</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -929,50 +901,46 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TRK-C09</t>
+          <t>TRK-008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>英雄赞歌（改名自英雄费歌）</t>
+          <t>长江之歌</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>南京保利剧院</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>广州大剧院</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>40</v>
+      </c>
+      <c r="E10" t="n">
+        <v>80</v>
       </c>
       <c r="F10" t="n">
-        <v>3520</v>
+        <v>3200</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>可发放</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>人工改名 原名英雄费歌 林老师要求改为英雄赞歌</t>
+          <t>时码错位：结束时间应为20:15:00，请核对</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>时码待核对</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>合唱团巡演餐补台账_CSV.csv</t>
+          <t>合唱团巡演曲目表.xlsx</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -985,31 +953,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TRK-C10</t>
+          <t>TRK-009</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>歌唱祖国</t>
+          <t>我的中国心</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>南京保利剧院</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
+          <t>广州大剧院</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" t="n">
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>4000</v>
+        <v>2800</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1018,7 +982,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>顺利记录 一切正常</t>
+          <t>人工改名：原名为'中国心'，林老师要求改为'我的中国心'</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1028,7 +992,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>合唱团巡演餐补台账_CSV.csv</t>
+          <t>合唱团巡演曲目表.xlsx</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1041,30 +1005,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TRK-001</t>
+          <t>TRK-010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>黄河大合唱</t>
+          <t>东方红</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>北京国家大剧院</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
+          <t>深圳保利剧院</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>42</v>
+      </c>
+      <c r="E12" t="n">
+        <v>80</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3360</v>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>可发放</t>
@@ -1072,7 +1034,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>林老师指定曲目，合唱团巡演餐补表重点关注</t>
+          <t>顺利记录，一切正常</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1087,7 +1049,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1095,30 +1057,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TRK-002</t>
+          <t>TRK-011</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>茉莉花</t>
+          <t>春天的故事</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>北京国家大剧院</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>30.0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>深圳保利剧院</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>33</v>
+      </c>
+      <c r="E13" t="n">
+        <v>80</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2640</v>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>待确认</t>
@@ -1126,12 +1086,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>旧版母带，2023年录音</t>
+          <t>需要人工确认授权，合唱团巡演餐补表重点</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>编号重复</t>
+          <t>授权待确认、信息不全</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1141,7 +1101,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1149,43 +1109,41 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TRK-002</t>
+          <t>TRK-012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>茉莉花</t>
+          <t>走进新时代</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>北京国家大剧院</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>32.0</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>深圳保利剧院</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>36</v>
+      </c>
+      <c r="E14" t="n">
+        <v>80</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2880</v>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>可发放</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>重复曲目编号TRK-002，注意核对</t>
+          <t>从曲目Excel补来的旧口径，原曲目名称已更新</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>编号重复</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1195,7 +1153,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1203,53 +1161,51 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TRK-003</t>
+          <t>TRK-C01</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>在希望的田野上</t>
+          <t>红旗颂</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>北京国家大剧院</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>38.0</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>杭州大剧院</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>48</v>
+      </c>
+      <c r="E15" t="n">
+        <v>80</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3840</v>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>可发放</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>缺授权，合唱团巡演餐补表待林老师确认</t>
+          <t>林老师指定开场曲</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>授权待确认、信息不全</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>合唱团巡演曲目表.xlsx</t>
+          <t>合唱团巡演餐补台账_CSV.csv</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1257,53 +1213,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TRK-004</t>
+          <t>TRK-C02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>歌唱祖国</t>
+          <t>我和我的祖国</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上海音乐厅</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>50.0</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>杭州大剧院</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>40</v>
+      </c>
+      <c r="E16" t="n">
+        <v>80</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3200</v>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>暂停</t>
+          <t>可发放</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>授权已过期，请更新</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>授权问题</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>合唱团巡演曲目表.xlsx</t>
+          <t>合唱团巡演餐补台账_CSV.csv</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1311,49 +1265,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TRK-005</t>
+          <t>TRK-C03</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>我爱你中国</t>
+          <t>团结就是力量</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>上海音乐厅</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>杭州大剧院</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>80</v>
+      </c>
+      <c r="F17" t="n">
+        <v>2800</v>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>可发放</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>参演人数空值，需要补全</t>
+          <t>旧版母带</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>信息不全</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>合唱团巡演曲目表.xlsx</t>
+          <t>合唱团巡演餐补台账_CSV.csv</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1361,26 +1317,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TRK-006</t>
+          <t>TRK-C04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>天路（女声版</t>
+          <t>保卫黄河</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>上海音乐厅</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>25.0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
+          <t>杭州大剧院</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>42</v>
+      </c>
+      <c r="E18" t="n">
+        <v>80</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3360</v>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>待确认</t>
@@ -1388,22 +1346,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>餐补标准空值</t>
+          <t>缺授权 合唱团巡演餐补表待确认</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>信息不全</t>
+          <t>授权待确认、信息不全</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>合唱团巡演曲目表.xlsx</t>
+          <t>合唱团巡演餐补台账_CSV.csv</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1411,53 +1369,51 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TRK-007</t>
+          <t>TRK-C05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>青藏高原</t>
+          <t>映山红</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>广州大剧院</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>28.0</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>南京保利剧院</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>38</v>
+      </c>
+      <c r="E19" t="n">
+        <v>80</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3040</v>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>可发放</t>
+          <t>暂停</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>旧版母带，2022年</t>
+          <t>授权过期</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>授权问题</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>合唱团巡演曲目表.xlsx</t>
+          <t>合唱团巡演餐补台账_CSV.csv</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1465,28 +1421,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TRK-008</t>
+          <t>TRK-C06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>长江之歌</t>
+          <t>美丽的草原我的家</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>广州大剧院</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
+          <t>南京保利剧院</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="n">
+        <v>80</v>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
@@ -1496,22 +1446,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>时码错位：结束时间应为20:15:00，请核对</t>
+          <t>参演人数空值</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>时码待核对</t>
+          <t>信息不全</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>合唱团巡演曲目表.xlsx</t>
+          <t>合唱团巡演餐补台账_CSV.csv</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1519,53 +1469,51 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TRK-009</t>
+          <t>TRK-C07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>我的中国心</t>
+          <t>在太行山上</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>广州大剧院</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>35.0</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>南京保利剧院</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>30</v>
+      </c>
+      <c r="E21" t="n">
+        <v>80</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2400</v>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>可发放</t>
+          <t>暂停</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>人工改名：原名为'中国心'，林老师要求改为'我的中国心'</t>
+          <t>旧版典藏</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>授权问题</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>合唱团巡演曲目表.xlsx</t>
+          <t>合唱团巡演餐补台账_CSV.csv</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1573,53 +1521,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TRK-010</t>
+          <t>TRK-C08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>东方红</t>
+          <t>游击队歌</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>深圳保利剧院</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>42.0</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
+          <t>南京保利剧院</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>36</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>可发放</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>顺利记录，一切正常</t>
+          <t>餐补标准空值</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>无</t>
+          <t>信息不全</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>合唱团巡演曲目表.xlsx</t>
+          <t>合唱团巡演餐补台账_CSV.csv</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1627,53 +1569,51 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TRK-011</t>
+          <t>TRK-C09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>春天的故事</t>
+          <t>英雄赞歌（改名自英雄费歌）</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>深圳保利剧院</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>33.0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
+          <t>南京保利剧院</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>44</v>
+      </c>
+      <c r="E23" t="n">
+        <v>80</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3520</v>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>可发放</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>需要人工确认授权，合唱团巡演餐补表重点</t>
+          <t>人工改名 原名英雄费歌 林老师要求改为英雄赞歌</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>授权待确认、信息不全</t>
+          <t>无</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>合唱团巡演曲目表.xlsx</t>
+          <t>合唱团巡演餐补台账_CSV.csv</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1681,30 +1621,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TRK-012</t>
+          <t>TRK-C10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>走进新时代</t>
+          <t>歌唱祖国</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>深圳保利剧院</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>80.0</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
+          <t>南京保利剧院</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>50</v>
+      </c>
+      <c r="E24" t="n">
+        <v>80</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4000</v>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>可发放</t>
@@ -1712,7 +1650,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>从曲目Excel补来的旧口径，原曲目名称已更新</t>
+          <t>顺利记录 一切正常</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1722,12 +1660,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>合唱团巡演曲目表.xlsx</t>
+          <t>合唱团巡演餐补台账_CSV.csv</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>11</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
